--- a/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>113</t>
+    <t>117</t>
   </si>
   <si>
     <t>Code</t>
@@ -878,6 +878,30 @@
   </si>
   <si>
     <t>La Passion-Clipperton</t>
+  </si>
+  <si>
+    <t>91352</t>
+  </si>
+  <si>
+    <t>Département D'Alger et Orleansville (91352)</t>
+  </si>
+  <si>
+    <t>92352</t>
+  </si>
+  <si>
+    <t>Département D'Oran et Bou Sfer (92352)</t>
+  </si>
+  <si>
+    <t>93352</t>
+  </si>
+  <si>
+    <t>Département de Constantine (93352)</t>
+  </si>
+  <si>
+    <t>94352</t>
+  </si>
+  <si>
+    <t>Sud de l'Algérie (94352)</t>
   </si>
   <si>
     <t>98000</t>
@@ -1347,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2720,6 +2744,54 @@
       </c>
       <c r="D114" s="2"/>
     </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20240628120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2024-06-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>117</t>
+    <t>113</t>
   </si>
   <si>
     <t>Code</t>
@@ -878,30 +878,6 @@
   </si>
   <si>
     <t>La Passion-Clipperton</t>
-  </si>
-  <si>
-    <t>91352</t>
-  </si>
-  <si>
-    <t>Département D'Alger et Orleansville (91352)</t>
-  </si>
-  <si>
-    <t>92352</t>
-  </si>
-  <si>
-    <t>Département D'Oran et Bou Sfer (92352)</t>
-  </si>
-  <si>
-    <t>93352</t>
-  </si>
-  <si>
-    <t>Département de Constantine (93352)</t>
-  </si>
-  <si>
-    <t>94352</t>
-  </si>
-  <si>
-    <t>Sud de l'Algérie (94352)</t>
   </si>
   <si>
     <t>98000</t>
@@ -1371,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2744,54 +2720,6 @@
       </c>
       <c r="D114" s="2"/>
     </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="D115" s="2"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="D116" s="2"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="D117" s="2"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="D118" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>113</t>
+    <t>117</t>
   </si>
   <si>
     <t>Code</t>
@@ -878,6 +878,30 @@
   </si>
   <si>
     <t>La Passion-Clipperton</t>
+  </si>
+  <si>
+    <t>91352</t>
+  </si>
+  <si>
+    <t>Alger</t>
+  </si>
+  <si>
+    <t>92352</t>
+  </si>
+  <si>
+    <t>Oran</t>
+  </si>
+  <si>
+    <t>93352</t>
+  </si>
+  <si>
+    <t>Constantine</t>
+  </si>
+  <si>
+    <t>94352</t>
+  </si>
+  <si>
+    <t>Territoires du sud de l'Algérie</t>
   </si>
   <si>
     <t>98000</t>
@@ -1347,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2720,6 +2744,54 @@
       </c>
       <c r="D114" s="2"/>
     </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
